--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>requestDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>requestAuthoredOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -498,7 +498,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t>requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +799,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1036,7 +1036,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1062,7 +1062,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1080,7 +1080,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1134,7 +1134,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1259,7 +1259,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1302,7 +1302,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1442,7 +1442,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用する。要約コード、または場所の非常に正確な定義への参照、あるいはその両方である可能性がある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1463,7 +1463,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1487,7 +1487,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1548,7 +1548,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit1.id</t>
@@ -1708,7 +1708,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.id</t>
@@ -1762,7 +1762,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1814,7 +1814,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2160,7 +2160,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="166.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="197.71875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2175,7 +2175,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.84375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>requestDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>requestAuthoredOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn}
 </t>
   </si>
   <si>
@@ -498,7 +498,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location}
 </t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t>requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester}
 </t>
   </si>
   <si>
@@ -705,7 +705,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -799,7 +799,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1036,7 +1036,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1062,7 +1062,7 @@
     <t>処方する製剤を表すコード。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationCode_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1080,7 +1080,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1108,7 +1108,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1134,7 +1134,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1259,7 +1259,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
@@ -1287,7 +1287,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1302,7 +1302,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|http://jpfhir.jp/fhir/core/StructureDefinition/JP_DiagnosticReport_Common)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection|1.3.0-dev)
+    <t xml:space="preserve">Reference(MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest_Injection)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(Device)
 </t>
   </si>
   <si>
@@ -1442,7 +1442,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用する。要約コード、または場所の非常に正確な定義への参照、あるいはその両方である可能性がある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1463,7 +1463,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1487,7 +1487,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1548,7 +1548,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit1.id</t>
@@ -1708,7 +1708,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.id</t>
@@ -1762,7 +1762,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity|4.0.1}</t>
+Quantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1814,7 +1814,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -1830,7 +1830,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -2160,7 +2160,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="197.71875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="166.0625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2175,7 +2175,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.84375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
